--- a/data/trans_orig/P41E_2023_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023_R-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que en el último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023</t>
+          <t>Población que en el último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023 (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10995</t>
+          <t>11025</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24204</t>
+          <t>24485</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9270</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20987</t>
+          <t>20324</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22920</t>
+          <t>22763</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39517</t>
+          <t>39171</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>256588</t>
+          <t>256307</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269797</t>
+          <t>269767</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>197535</t>
+          <t>198198</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>209252</t>
+          <t>209336</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>459797</t>
+          <t>460143</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>476394</t>
+          <t>476551</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>17046</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34999</t>
+          <t>33503</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19235</t>
+          <t>19521</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28605</t>
+          <t>27538</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49976</t>
+          <t>47694</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>199669</t>
+          <t>201165</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>216836</t>
+          <t>217622</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>172258</t>
+          <t>171972</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>183672</t>
+          <t>183469</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>376185</t>
+          <t>378467</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>397556</t>
+          <t>398623</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10059</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71394</t>
+          <t>71830</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20404</t>
+          <t>20345</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17014</t>
+          <t>16027</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88924</t>
+          <t>89060</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>401952</t>
+          <t>401516</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>463287</t>
+          <t>464045</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60061</t>
+          <t>60120</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70782</t>
+          <t>70379</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>464887</t>
+          <t>464751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>536797</t>
+          <t>537784</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48689</t>
+          <t>48490</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74912</t>
+          <t>74225</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10559</t>
+          <t>9880</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48345</t>
+          <t>49239</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48097</t>
+          <t>45142</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116393</t>
+          <t>117359</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>398150</t>
+          <t>398837</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>424373</t>
+          <t>424572</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>513044</t>
+          <t>512150</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>550830</t>
+          <t>551509</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>918058</t>
+          <t>917092</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>986354</t>
+          <t>989309</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25053</t>
+          <t>25369</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43842</t>
+          <t>44004</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51283</t>
+          <t>50898</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71383</t>
+          <t>71265</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81812</t>
+          <t>81011</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>108974</t>
+          <t>107689</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>181728</t>
+          <t>181566</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200517</t>
+          <t>200201</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>267093</t>
+          <t>267211</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>287193</t>
+          <t>287578</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>455072</t>
+          <t>456357</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>482234</t>
+          <t>483035</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,64%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14344</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>42910</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64640</t>
+          <t>64157</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48560</t>
+          <t>48237</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72180</t>
+          <t>72191</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31594</t>
+          <t>31507</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44712</t>
+          <t>44138</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>191767</t>
+          <t>192250</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>213349</t>
+          <t>213497</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>230165</t>
+          <t>230154</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>253785</t>
+          <t>254108</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,05%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>110502</t>
+          <t>103718</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>208013</t>
+          <t>211325</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>122857</t>
+          <t>107258</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>216800</t>
+          <t>216208</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>273208</t>
+          <t>261276</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>414807</t>
+          <t>411557</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1525363</t>
+          <t>1522051</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1622874</t>
+          <t>1629658</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1429952</t>
+          <t>1430544</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1523895</t>
+          <t>1539494</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2965321</t>
+          <t>2968571</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3106920</t>
+          <t>3118852</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41E_2023_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023_R-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16245</t>
+          <t>17644</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11025</t>
+          <t>11768</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24485</t>
+          <t>26170</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13947</t>
+          <t>15544</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20324</t>
+          <t>22589</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>30193</t>
+          <t>33188</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22763</t>
+          <t>24117</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39171</t>
+          <t>43036</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>264547</t>
+          <t>290386</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>256307</t>
+          <t>281860</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269767</t>
+          <t>296262</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>204575</t>
+          <t>223635</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>198198</t>
+          <t>216590</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>209336</t>
+          <t>229033</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>469121</t>
+          <t>514021</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>460143</t>
+          <t>504173</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>476551</t>
+          <t>523092</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>280792</t>
+          <t>308030</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>280792</t>
+          <t>308030</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>280792</t>
+          <t>308030</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>218522</t>
+          <t>239179</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>218522</t>
+          <t>239179</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>218522</t>
+          <t>239179</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>499314</t>
+          <t>547209</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>499314</t>
+          <t>547209</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>499314</t>
+          <t>547209</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24886</t>
+          <t>26413</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17046</t>
+          <t>18429</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33503</t>
+          <t>36704</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12488</t>
+          <t>13778</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>8734</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19521</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>37374</t>
+          <t>40191</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27538</t>
+          <t>31418</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47694</t>
+          <t>52240</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>209782</t>
+          <t>225454</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>201165</t>
+          <t>215163</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>217622</t>
+          <t>233438</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>179005</t>
+          <t>196690</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>171972</t>
+          <t>189583</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>183469</t>
+          <t>201734</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>388787</t>
+          <t>422144</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>378467</t>
+          <t>410095</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>398623</t>
+          <t>430917</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,2%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>234668</t>
+          <t>251867</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>234668</t>
+          <t>251867</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>234668</t>
+          <t>251867</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>191493</t>
+          <t>210468</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>191493</t>
+          <t>210468</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>191493</t>
+          <t>210468</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>426161</t>
+          <t>462335</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>426161</t>
+          <t>462335</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>426161</t>
+          <t>462335</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>31826</t>
+          <t>33611</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>25100</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71830</t>
+          <t>44507</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14452</t>
+          <t>15922</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>10718</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20345</t>
+          <t>22341</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>46277</t>
+          <t>49533</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16027</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89060</t>
+          <t>62213</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>441520</t>
+          <t>217293</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>401516</t>
+          <t>206397</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>464045</t>
+          <t>225804</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>66013</t>
+          <t>73827</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60120</t>
+          <t>67408</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70379</t>
+          <t>79031</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>507534</t>
+          <t>291119</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>464751</t>
+          <t>278439</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>537784</t>
+          <t>301996</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>473346</t>
+          <t>250904</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>473346</t>
+          <t>250904</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>473346</t>
+          <t>250904</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>80465</t>
+          <t>89749</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>80465</t>
+          <t>89749</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>80465</t>
+          <t>89749</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>553811</t>
+          <t>340652</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>553811</t>
+          <t>340652</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>553811</t>
+          <t>340652</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60487</t>
+          <t>64955</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48490</t>
+          <t>53030</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74225</t>
+          <t>78792</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27834</t>
+          <t>29740</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9880</t>
+          <t>21661</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49239</t>
+          <t>40056</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>88321</t>
+          <t>94695</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45142</t>
+          <t>79844</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>117359</t>
+          <t>111263</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>412575</t>
+          <t>455247</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>398837</t>
+          <t>441410</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>424572</t>
+          <t>467172</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>533555</t>
+          <t>365930</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>512150</t>
+          <t>355614</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>551509</t>
+          <t>374009</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>946130</t>
+          <t>821177</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>917092</t>
+          <t>804609</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>989309</t>
+          <t>836028</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>473062</t>
+          <t>520202</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>473062</t>
+          <t>520202</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>473062</t>
+          <t>520202</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>561389</t>
+          <t>395670</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>561389</t>
+          <t>395670</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>561389</t>
+          <t>395670</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1034451</t>
+          <t>915872</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1034451</t>
+          <t>915872</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1034451</t>
+          <t>915872</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,22 +2097,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>33774</t>
+          <t>37335</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25369</t>
+          <t>28633</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44004</t>
+          <t>48860</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>61038</t>
+          <t>66193</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50898</t>
+          <t>54519</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71265</t>
+          <t>76977</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>94813</t>
+          <t>103528</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81011</t>
+          <t>88550</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107689</t>
+          <t>119089</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -2210,27 +2210,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>191796</t>
+          <t>217171</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>181566</t>
+          <t>205646</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200201</t>
+          <t>225873</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>277438</t>
+          <t>310159</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>267211</t>
+          <t>299375</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>287578</t>
+          <t>321833</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>469233</t>
+          <t>527330</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>456357</t>
+          <t>511769</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>483035</t>
+          <t>542308</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>225570</t>
+          <t>254506</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>225570</t>
+          <t>254506</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>225570</t>
+          <t>254506</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>338476</t>
+          <t>376352</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>338476</t>
+          <t>376352</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>338476</t>
+          <t>376352</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>564046</t>
+          <t>630858</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>564046</t>
+          <t>630858</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>564046</t>
+          <t>630858</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>5214</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>12894</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>53348</t>
+          <t>59461</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42910</t>
+          <t>47781</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64157</t>
+          <t>72017</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>59163</t>
+          <t>64675</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48237</t>
+          <t>52935</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72191</t>
+          <t>80758</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,86%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>40123</t>
+          <t>40135</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31507</t>
+          <t>32455</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44138</t>
+          <t>44003</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>203059</t>
+          <t>220101</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>192250</t>
+          <t>207545</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>213497</t>
+          <t>231781</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>243182</t>
+          <t>260236</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>230154</t>
+          <t>244153</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>254108</t>
+          <t>271976</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,71%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>45938</t>
+          <t>45349</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45938</t>
+          <t>45349</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45938</t>
+          <t>45349</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256407</t>
+          <t>279562</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256407</t>
+          <t>279562</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256407</t>
+          <t>279562</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>302345</t>
+          <t>324911</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>302345</t>
+          <t>324911</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>302345</t>
+          <t>324911</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>173033</t>
+          <t>185172</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>103718</t>
+          <t>163574</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>211325</t>
+          <t>210903</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>183107</t>
+          <t>200639</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>107258</t>
+          <t>179884</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>216208</t>
+          <t>221202</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>356140</t>
+          <t>385811</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>261276</t>
+          <t>353011</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>411557</t>
+          <t>416635</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1560343</t>
+          <t>1445685</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1522051</t>
+          <t>1419954</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1629658</t>
+          <t>1467283</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1463645</t>
+          <t>1390341</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1430544</t>
+          <t>1369778</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1539494</t>
+          <t>1411096</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3023988</t>
+          <t>2836026</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2968571</t>
+          <t>2805202</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3118852</t>
+          <t>2868826</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>89,04%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1733376</t>
+          <t>1630857</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1733376</t>
+          <t>1630857</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1733376</t>
+          <t>1630857</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1646752</t>
+          <t>1590980</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1646752</t>
+          <t>1590980</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1646752</t>
+          <t>1590980</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3380128</t>
+          <t>3221837</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3380128</t>
+          <t>3221837</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3380128</t>
+          <t>3221837</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">

--- a/data/trans_orig/P41E_2023_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023_R-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que en el último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023 (tasa de respuesta: 69,32%)</t>
+          <t>Población que en el último año declara que sus relaciones sexuales no han sido satisfactorias para ambas partes (bastante en desacuerdo/totalmente en desacuerdo) en 2023 (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
